--- a/example_run/quotes_received.xlsx
+++ b/example_run/quotes_received.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>No saved email contact or portal login for 'ElectroConn' - this source hasn't been explored yet. Needs manual outreach before qualification or an RFQ can proceed.</t>
+          <t>'ElectroConn' is not yet an approved vendor (ISO 9001 status: Unknown) - needs qualification review before an RFQ can be sent.</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>No saved email contact or portal login for 'MeanTech' - this source hasn't been explored yet. Needs manual outreach before qualification or an RFQ can proceed.</t>
+          <t>'MeanTech' is not yet an approved vendor (ISO 9001 status: Unknown) - needs qualification review before an RFQ can be sent.</t>
         </is>
       </c>
     </row>
@@ -717,29 +717,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Email content received for RESIN8-RFQ-0004 but quote fields could not be extracted (no LLM access) - needs manual read: Thanks for reaching out. For part 1234K56 (Aluminum mounting bracket for NEMA 17 servo motors), qty 4: unit price $8.75, extended price $35.00. In stock, ships in 2 business days. Quote valid 30 days </t>
+          <t>Distributor part - pricing should come from a Stage 2 catalog query, not an RFQ. Skipped here.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Email content received for RESIN8-RFQ-0006 but quote fields could not be extracted (no LLM access) - needs manual read: We can supply the am-3103a gearbox. Note: minimum order quantity is 5 units, your request was for 2 - happy to quote at 5 if that works. Unit price at MOQ $42.00, extended $210.00. Lead time 3 weeks, </t>
+          <t>Distributor part - pricing should come from a Stage 2 catalog query, not an RFQ. Skipped here.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Email content received for RESIN8-RFQ-0004 but quote fields could not be extracted (no LLM access) - needs manual read: Thanks for reaching out. For part 1234K56 (Aluminum mounting bracket for NEMA 17 servo motors), qty 4: unit price $8.75, extended price $35.00. In stock, ships in 2 business days. Quote valid 30 days </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Email content received for RESIN8-RFQ-0006 but quote fields could not be extracted (no LLM access) - needs manual read: We can supply the am-3103a gearbox. Note: minimum order quantity is 5 units, your request was for 2 - happy to quote at 5 if that works. Unit price at MOQ $42.00, extended $210.00. Lead time 3 weeks, </t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
         <v>8</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Portal content received for 8 but quote fields could not be extracted (no LLM access) - needs manual read: My Account &gt; Quotes
 Quote #Q-88213 - LM6UU Linear ball bearing, 6mm bore
